--- a/Hoadon/HD2026/HDVao/2/3502550210_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDVao/2/3502550210_HDDienTuMayTinhTien.xlsx
@@ -454,37 +454,37 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C26MTT</t>
+          <t>C26MTQ</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>07/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>051076001913</t>
+          <t>0302478297</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CÀ PHÊ THÁI NGUYÊN</t>
+          <t>CÔNG TY TNHH TRẦN QUANG VIỆT NAM</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Tổ 15 khu phố Hải Dinh, Phường Long Hương, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+          <t>621 Xô Viết Nghệ Tĩnh, Phường Bình Thạnh, Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -498,13 +498,17 @@
         </is>
       </c>
       <c r="K9" s="6"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
+      <c r="L9" s="13" t="n">
+        <v>7.2601852E7</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>5808148.0</v>
+      </c>
       <c r="N9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>4500000.0</v>
+        <v>7.841E7</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -533,27 +537,27 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>07/02/2026</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>077082002684</t>
+          <t>051076001913</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG HOÀI MINH ANH</t>
+          <t>HỘ KINH DOANH CÀ PHÊ THÁI NGUYÊN</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Số 41Y, khu phố Long Phượng, Xã Long Điền, TP Hồ Chí Minh</t>
+          <t>Tổ 15 khu phố Hải Dinh, Phường Long Hương, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -573,7 +577,7 @@
         <v>0.0</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>3089000.0</v>
+        <v>4500000.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -597,32 +601,32 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C26MAA</t>
+          <t>C26MTT</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>082082001130</t>
+          <t>077082002684</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH MAI SAO MAI.</t>
+          <t>HỘ KINH DOANH CỬA HÀNG HOÀI MINH ANH</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>1/20, Nguyễn Văn Nguyễn, Khu phố 19, Phường Mỹ Tho, Tỉnh Đồng Tháp, Việt Nam</t>
+          <t>Số 41Y, khu phố Long Phượng, Xã Long Điền, TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -642,7 +646,7 @@
         <v>0.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>925000.0</v>
+        <v>3089000.0</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -661,37 +665,37 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C26MRV</t>
+          <t>C26MAA</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>01/02/2026</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>082082001130</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>HỘ KINH DOANH MAI SAO MAI.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>1/20, Nguyễn Văn Nguyễn, Khu phố 19, Phường Mỹ Tho, Tỉnh Đồng Tháp, Việt Nam</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
@@ -705,17 +709,13 @@
         </is>
       </c>
       <c r="K12" s="6"/>
-      <c r="L12" s="13" t="n">
-        <v>1384279.0</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>110742.0</v>
-      </c>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
       <c r="N12" s="13" t="n">
-        <v>35321.0</v>
+        <v>0.0</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>1495021.0</v>
+        <v>925000.0</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -779,16 +779,16 @@
       </c>
       <c r="K13" s="6"/>
       <c r="L13" s="13" t="n">
-        <v>3229922.0</v>
+        <v>1384279.0</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>258394.0</v>
+        <v>110742.0</v>
       </c>
       <c r="N13" s="13" t="n">
-        <v>77528.0</v>
+        <v>35321.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>3488316.0</v>
+        <v>1495021.0</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -852,16 +852,16 @@
       </c>
       <c r="K14" s="6"/>
       <c r="L14" s="13" t="n">
-        <v>1075511.0</v>
+        <v>3229922.0</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>86041.0</v>
+        <v>258394.0</v>
       </c>
       <c r="N14" s="13" t="n">
-        <v>143889.0</v>
+        <v>77528.0</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>1161552.0</v>
+        <v>3488316.0</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -890,12 +890,12 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -925,16 +925,16 @@
       </c>
       <c r="K15" s="6"/>
       <c r="L15" s="13" t="n">
-        <v>1553524.0</v>
+        <v>1075511.0</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>124282.0</v>
+        <v>86041.0</v>
       </c>
       <c r="N15" s="13" t="n">
-        <v>28476.0</v>
+        <v>143889.0</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>1677806.0</v>
+        <v>1161552.0</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
@@ -963,12 +963,12 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>7386</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>07/02/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -998,16 +998,16 @@
       </c>
       <c r="K16" s="6"/>
       <c r="L16" s="13" t="n">
-        <v>7925321.0</v>
+        <v>1553524.0</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>634026.0</v>
+        <v>124282.0</v>
       </c>
       <c r="N16" s="13" t="n">
-        <v>22379.0</v>
+        <v>28476.0</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>8559347.0</v>
+        <v>1677806.0</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>7728</t>
+          <t>7386</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>09/02/2026</t>
+          <t>07/02/2026</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1066,21 +1066,21 @@
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K17" s="6"/>
       <c r="L17" s="13" t="n">
-        <v>3.4027778E7</v>
+        <v>7925321.0</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>2722222.0</v>
+        <v>634026.0</v>
       </c>
       <c r="N17" s="13" t="n">
-        <v>2032222.0</v>
+        <v>22379.0</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>3.675E7</v>
+        <v>8559347.0</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>09/02/2026</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1139,21 +1139,21 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K18" s="6"/>
       <c r="L18" s="13" t="n">
-        <v>6041157.0</v>
+        <v>3.4027778E7</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>483293.0</v>
+        <v>2722222.0</v>
       </c>
       <c r="N18" s="13" t="n">
-        <v>226603.0</v>
+        <v>2032222.0</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>6524450.0</v>
+        <v>3.675E7</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>7991</t>
+          <t>7990</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1217,16 +1217,16 @@
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="13" t="n">
-        <v>1513509.0</v>
+        <v>6041157.0</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>121081.0</v>
+        <v>483293.0</v>
       </c>
       <c r="N19" s="13" t="n">
-        <v>34191.0</v>
+        <v>226603.0</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>1634590.0</v>
+        <v>6524450.0</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
@@ -1250,32 +1250,32 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>C26MTK</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>3502242819</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THOẠI KHANG</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
@@ -1290,14 +1290,16 @@
       </c>
       <c r="K20" s="6"/>
       <c r="L20" s="13" t="n">
-        <v>4260000.0</v>
+        <v>1513509.0</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>426000.0</v>
-      </c>
-      <c r="N20" s="13"/>
+        <v>121081.0</v>
+      </c>
+      <c r="N20" s="13" t="n">
+        <v>34191.0</v>
+      </c>
       <c r="O20" s="13" t="n">
-        <v>4686000.0</v>
+        <v>1634590.0</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
@@ -1321,32 +1323,32 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>C26MTK</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>8574</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>3502242819</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THOẠI KHANG</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -1361,14 +1363,16 @@
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="13" t="n">
-        <v>4260000.0</v>
+        <v>1692000.0</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>426000.0</v>
-      </c>
-      <c r="N21" s="13"/>
+        <v>135360.0</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O21" s="13" t="n">
-        <v>4686000.0</v>
+        <v>1827360.0</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
@@ -1392,32 +1396,32 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>C26MTK</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>3502242819</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THOẠI KHANG</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
@@ -1432,14 +1436,16 @@
       </c>
       <c r="K22" s="6"/>
       <c r="L22" s="13" t="n">
-        <v>4260000.0</v>
+        <v>2191945.0</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>426000.0</v>
-      </c>
-      <c r="N22" s="13"/>
+        <v>175356.0</v>
+      </c>
+      <c r="N22" s="13" t="n">
+        <v>52455.0</v>
+      </c>
       <c r="O22" s="13" t="n">
-        <v>4686000.0</v>
+        <v>2367301.0</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
@@ -1463,32 +1469,32 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -1498,21 +1504,21 @@
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K23" s="6"/>
       <c r="L23" s="13" t="n">
-        <v>2.0368181E7</v>
+        <v>4.6759259E7</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>2036819.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="N23" s="13" t="n">
-        <v>0.0</v>
+        <v>4696741.0</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>2.2405E7</v>
+        <v>5.05E7</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
@@ -1536,32 +1542,32 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>08/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
@@ -1576,16 +1582,16 @@
       </c>
       <c r="K24" s="6"/>
       <c r="L24" s="13" t="n">
-        <v>3.309091E7</v>
+        <v>4850700.0</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>3309091.0</v>
+        <v>388056.0</v>
       </c>
       <c r="N24" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>3.6400001E7</v>
+        <v>5238756.0</v>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
@@ -1609,32 +1615,32 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>09/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
@@ -1649,16 +1655,16 @@
       </c>
       <c r="K25" s="6"/>
       <c r="L25" s="13" t="n">
-        <v>2.7984664E7</v>
+        <v>5879287.0</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>2755336.0</v>
+        <v>470343.0</v>
       </c>
       <c r="N25" s="13" t="n">
-        <v>0.0</v>
+        <v>137113.0</v>
       </c>
       <c r="O25" s="13" t="n">
-        <v>3.074E7</v>
+        <v>6349630.0</v>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
@@ -1682,32 +1688,32 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -1722,16 +1728,16 @@
       </c>
       <c r="K26" s="6"/>
       <c r="L26" s="13" t="n">
-        <v>6.8706649E7</v>
+        <v>6.8709259E7</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>6795351.0</v>
+        <v>5496741.0</v>
       </c>
       <c r="N26" s="13" t="n">
-        <v>0.0</v>
+        <v>6729941.0</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>7.5502E7</v>
+        <v>7.4206E7</v>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
@@ -1755,32 +1761,32 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
@@ -1795,16 +1801,16 @@
       </c>
       <c r="K27" s="6"/>
       <c r="L27" s="13" t="n">
-        <v>3.0833333E7</v>
+        <v>3470700.0</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>2466667.0</v>
+        <v>277656.0</v>
       </c>
       <c r="N27" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>3.33E7</v>
+        <v>3748356.0</v>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
@@ -1828,32 +1834,32 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>C26MDH</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>08/02/2026</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>3502399055</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -1868,16 +1874,16 @@
       </c>
       <c r="K28" s="6"/>
       <c r="L28" s="13" t="n">
-        <v>2863657.0</v>
+        <v>2214000.0</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>229093.0</v>
+        <v>177120.0</v>
       </c>
       <c r="N28" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>3092750.0</v>
+        <v>2391120.0</v>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
@@ -1901,12 +1907,12 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MTK</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>517</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -1916,17 +1922,17 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502242819</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THOẠI KHANG</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
@@ -1941,16 +1947,14 @@
       </c>
       <c r="K29" s="6"/>
       <c r="L29" s="13" t="n">
-        <v>1712965.0</v>
+        <v>4260000.0</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>137035.0</v>
-      </c>
-      <c r="N29" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>426000.0</v>
+      </c>
+      <c r="N29" s="13"/>
       <c r="O29" s="13" t="n">
-        <v>1850000.0</v>
+        <v>4686000.0</v>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
@@ -1974,12 +1978,12 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MTK</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>546</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -1989,17 +1993,17 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502242819</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THOẠI KHANG</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -2014,16 +2018,14 @@
       </c>
       <c r="K30" s="6"/>
       <c r="L30" s="13" t="n">
-        <v>1.9722222E7</v>
+        <v>4260000.0</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>1577778.0</v>
-      </c>
-      <c r="N30" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>426000.0</v>
+      </c>
+      <c r="N30" s="13"/>
       <c r="O30" s="13" t="n">
-        <v>2.13E7</v>
+        <v>4686000.0</v>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
@@ -2047,32 +2049,32 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MTK</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>564</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502242819</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THOẠI KHANG</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
@@ -2087,16 +2089,14 @@
       </c>
       <c r="K31" s="6"/>
       <c r="L31" s="13" t="n">
-        <v>7339815.0</v>
+        <v>4260000.0</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>587185.0</v>
-      </c>
-      <c r="N31" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>426000.0</v>
+      </c>
+      <c r="N31" s="13"/>
       <c r="O31" s="13" t="n">
-        <v>7927000.0</v>
+        <v>4686000.0</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
@@ -2120,32 +2120,32 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>C26MBA</t>
+          <t>C26MHT</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>693</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>3703329361</t>
+          <t>3502324074</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BẢO ANH FOOD</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HƯƠNG THỊNH PHÁT</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Thửa đất 1515, tờ bản đồ số 14, Đường Trần Công Anh, Tổ 1, Khu phố Mỹ Hiệp, Phường Tân Đông Hiệp, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>69 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
@@ -2160,23 +2160,1337 @@
       </c>
       <c r="K32" s="6"/>
       <c r="L32" s="13" t="n">
-        <v>2868000.0</v>
+        <v>2.3324E8</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>214800.0</v>
+        <v>2.3324E7</v>
       </c>
       <c r="N32" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O32" s="13" t="n">
+        <v>2.56564E8</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>C26MHT</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>3502324074</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HƯƠNG THỊNH PHÁT</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>69 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K33" s="6"/>
+      <c r="L33" s="13" t="n">
+        <v>7177140.0</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>717714.0</v>
+      </c>
+      <c r="N33" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O33" s="13" t="n">
+        <v>7894854.0</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>05/02/2026</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K34" s="6"/>
+      <c r="L34" s="13" t="n">
+        <v>2.0368181E7</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>2036819.0</v>
+      </c>
+      <c r="N34" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O34" s="13" t="n">
+        <v>2.2405E7</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>08/02/2026</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K35" s="6"/>
+      <c r="L35" s="13" t="n">
+        <v>3.309091E7</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>3309091.0</v>
+      </c>
+      <c r="N35" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O35" s="13" t="n">
+        <v>3.6400001E7</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K36" s="6"/>
+      <c r="L36" s="13" t="n">
+        <v>2.7984664E7</v>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>2755336.0</v>
+      </c>
+      <c r="N36" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O36" s="13" t="n">
+        <v>3.074E7</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K37" s="6"/>
+      <c r="L37" s="13" t="n">
+        <v>6.8706649E7</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>6795351.0</v>
+      </c>
+      <c r="N37" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O37" s="13" t="n">
+        <v>7.5502E7</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K38" s="6"/>
+      <c r="L38" s="13" t="n">
+        <v>3.0833333E7</v>
+      </c>
+      <c r="M38" s="13" t="n">
+        <v>2466667.0</v>
+      </c>
+      <c r="N38" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O38" s="13" t="n">
+        <v>3.33E7</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>11/02/2026</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K39" s="6"/>
+      <c r="L39" s="13" t="n">
+        <v>1.9263636E7</v>
+      </c>
+      <c r="M39" s="13" t="n">
+        <v>1926364.0</v>
+      </c>
+      <c r="N39" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O39" s="13" t="n">
+        <v>2.119E7</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>12/02/2026</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K40" s="6"/>
+      <c r="L40" s="13" t="n">
+        <v>1.7239259E7</v>
+      </c>
+      <c r="M40" s="13" t="n">
+        <v>1688741.0</v>
+      </c>
+      <c r="N40" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O40" s="13" t="n">
+        <v>1.8928E7</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K41" s="6"/>
+      <c r="L41" s="13" t="n">
+        <v>6.3336364E7</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>6333636.0</v>
+      </c>
+      <c r="N41" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O41" s="13" t="n">
+        <v>6.967E7</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>26/02/2026</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K42" s="6"/>
+      <c r="L42" s="13" t="n">
+        <v>1563636.0</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>156364.0</v>
+      </c>
+      <c r="N42" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O42" s="13" t="n">
+        <v>1720000.0</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>C26MDH</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>08/02/2026</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K43" s="6"/>
+      <c r="L43" s="13" t="n">
+        <v>2863657.0</v>
+      </c>
+      <c r="M43" s="13" t="n">
+        <v>229093.0</v>
+      </c>
+      <c r="N43" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O43" s="13" t="n">
+        <v>3092750.0</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>C26MDH</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K44" s="6"/>
+      <c r="L44" s="13" t="n">
+        <v>3402314.0</v>
+      </c>
+      <c r="M44" s="13" t="n">
+        <v>272186.0</v>
+      </c>
+      <c r="N44" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O44" s="13" t="n">
+        <v>3674500.0</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>C26MYY</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>785</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>26/02/2026</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>3502474552</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K45" s="6"/>
+      <c r="L45" s="13" t="n">
+        <v>5454547.0</v>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>545455.0</v>
+      </c>
+      <c r="N45" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O45" s="13" t="n">
+        <v>6000002.0</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>C26MYY</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>11/02/2026</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>3502483525</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K46" s="6"/>
+      <c r="L46" s="13" t="n">
+        <v>5.2727272E7</v>
+      </c>
+      <c r="M46" s="13" t="n">
+        <v>5272727.0</v>
+      </c>
+      <c r="N46" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O46" s="13" t="n">
+        <v>5.7999999E7</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K47" s="6"/>
+      <c r="L47" s="13" t="n">
+        <v>1712965.0</v>
+      </c>
+      <c r="M47" s="13" t="n">
+        <v>137035.0</v>
+      </c>
+      <c r="N47" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O47" s="13" t="n">
+        <v>1850000.0</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K48" s="6"/>
+      <c r="L48" s="13" t="n">
+        <v>1.9722222E7</v>
+      </c>
+      <c r="M48" s="13" t="n">
+        <v>1577778.0</v>
+      </c>
+      <c r="N48" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O48" s="13" t="n">
+        <v>2.13E7</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>43.0</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K49" s="6"/>
+      <c r="L49" s="13" t="n">
+        <v>7339815.0</v>
+      </c>
+      <c r="M49" s="13" t="n">
+        <v>587185.0</v>
+      </c>
+      <c r="N49" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O49" s="13" t="n">
+        <v>7927000.0</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>C26MBA</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>05/02/2026</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>3703329361</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH BẢO ANH FOOD</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Thửa đất 1515, tờ bản đồ số 14, Đường Trần Công Anh, Tổ 1, Khu phố Mỹ Hiệp, Phường Tân Đông Hiệp, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K50" s="6"/>
+      <c r="L50" s="13" t="n">
+        <v>2868000.0</v>
+      </c>
+      <c r="M50" s="13" t="n">
+        <v>214800.0</v>
+      </c>
+      <c r="N50" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O50" s="13" t="n">
         <v>3082800.0</v>
       </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>
